--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$177</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6350" uniqueCount="424">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1084,6 +1084,240 @@
   </si>
   <si>
     <t>Bundle.entry:Medikationsplaneintrag.response.outcome</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient</t>
+  </si>
+  <si>
+    <t>Patient</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SubjectOfCare Client Resident
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient}
+</t>
+  </si>
+  <si>
+    <t>Information about an individual or animal receiving health care services</t>
+  </si>
+  <si>
+    <t>Demographics and other administrative information about an individual or animal receiving care or other health-related services.</t>
+  </si>
+  <si>
+    <t>Patient[classCode=PAT]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.recordTarget.patientRole</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Patient.response.outcome</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.resource</t>
+  </si>
+  <si>
+    <t>Practitioner {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner}
+Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole}Patient {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient}</t>
+  </si>
+  <si>
+    <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
+  </si>
+  <si>
+    <t>A person who is directly or indirectly involved in the provisioning of healthcare.</t>
+  </si>
+  <si>
+    <t>PRD (as one example)</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Source.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -1427,20 +1661,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN113"/>
+  <dimension ref="A1:AN177"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.44140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.37109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="24.67578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.2734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="218.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -14168,9 +14402,11 @@
         <v>341</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C113" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="D113" t="s" s="2">
         <v>21</v>
       </c>
@@ -14191,20 +14427,16 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>342</v>
+        <v>145</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>343</v>
+        <v>176</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>21</v>
       </c>
@@ -14252,35 +14484,7285 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>341</v>
+        <v>175</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ113" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AK113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN113" t="s" s="2">
+      <c r="AK117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O125" s="2"/>
+      <c r="P125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N144" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O144" s="2"/>
+      <c r="P144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C145" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="D145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147" hidden="true">
+      <c r="A147" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148" hidden="true">
+      <c r="A148" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149" hidden="true">
+      <c r="A149" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N149" s="2"/>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="150" hidden="true">
+      <c r="A150" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="O150" s="2"/>
+      <c r="P150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="151" hidden="true">
+      <c r="A151" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN154" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL155" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM155" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN155" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="O156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM156" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN156" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" hidden="true">
+      <c r="A157" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN157" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
+      <c r="P158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM158" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN158" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL159" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM159" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN159" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="160" hidden="true">
+      <c r="A160" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL160" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM160" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN160" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="161" hidden="true">
+      <c r="A161" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N161" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O161" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM161" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN161" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="162" hidden="true">
+      <c r="A162" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N162" s="2"/>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN162" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="163" hidden="true">
+      <c r="A163" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E163" s="2"/>
+      <c r="F163" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K163" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M163" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O163" s="2"/>
+      <c r="P163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q163" s="2"/>
+      <c r="R163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM163" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN163" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="164" hidden="true">
+      <c r="A164" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E164" s="2"/>
+      <c r="F164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L164" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N164" s="2"/>
+      <c r="O164" s="2"/>
+      <c r="P164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q164" s="2"/>
+      <c r="R164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM164" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN164" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="165" hidden="true">
+      <c r="A165" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E165" s="2"/>
+      <c r="F165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
+      <c r="P165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q165" s="2"/>
+      <c r="R165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN165" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="166" hidden="true">
+      <c r="A166" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N166" s="2"/>
+      <c r="O166" s="2"/>
+      <c r="P166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN166" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="167" hidden="true">
+      <c r="A167" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
+      <c r="P167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168" hidden="true">
+      <c r="A168" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" hidden="true">
+      <c r="A169" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
+      <c r="P169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170" hidden="true">
+      <c r="A170" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O170" s="2"/>
+      <c r="P170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL170" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="P171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="172" hidden="true">
+      <c r="A172" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N172" s="2"/>
+      <c r="O172" s="2"/>
+      <c r="P172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N173" s="2"/>
+      <c r="O173" s="2"/>
+      <c r="P173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O174" s="2"/>
+      <c r="P174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="175" hidden="true">
+      <c r="A175" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM175" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN175" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="176" hidden="true">
+      <c r="A176" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM176" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN176" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="177" hidden="true">
+      <c r="A177" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G177" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J177" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K177" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L177" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M177" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O177" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="P177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q177" s="2"/>
+      <c r="R177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF177" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG177" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM177" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN177" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN113">
+  <autoFilter ref="A1:AN177">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14290,7 +21772,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI112">
+  <conditionalFormatting sqref="A2:AI176">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6350" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6350" uniqueCount="425">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -575,6 +575,9 @@
     <t>Bundle.entry</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Entry in the bundle - will have a resource or information</t>
   </si>
   <si>
@@ -1205,28 +1208,28 @@
     <t>Bundle.entry:Patient.response.outcome</t>
   </si>
   <si>
-    <t>Bundle.entry:Source</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.link</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.fullUrl</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.resource</t>
+    <t>Bundle.entry:Authors</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.resource</t>
   </si>
   <si>
     <t>Practitioner {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner}
@@ -1245,79 +1248,79 @@
     <t>Role</t>
   </si>
   <si>
-    <t>Bundle.entry:Source.search</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.search.mode</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.search.score</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.method</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.url</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.ifMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.status</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.location</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.etag</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.lastModified</t>
-  </si>
-  <si>
-    <t>Bundle.entry:Source.response.outcome</t>
+    <t>Bundle.entry:Authors.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:Authors.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>
@@ -3542,7 +3545,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>87</v>
+        <v>176</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -3560,10 +3563,10 @@
         <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3602,14 +3605,14 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>175</v>
@@ -3624,7 +3627,7 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -3641,10 +3644,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3753,10 +3756,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3867,10 +3870,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3983,10 +3986,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4012,10 +4015,10 @@
         <v>21</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4066,7 +4069,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4095,10 +4098,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4106,7 +4109,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>87</v>
@@ -4124,13 +4127,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4180,7 +4183,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4209,10 +4212,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4235,13 +4238,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4292,7 +4295,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4321,10 +4324,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4350,10 +4353,10 @@
         <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4404,7 +4407,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4413,7 +4416,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4433,10 +4436,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4545,10 +4548,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4659,10 +4662,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4775,10 +4778,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4804,13 +4807,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4839,10 +4842,10 @@
         <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4860,7 +4863,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4889,10 +4892,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4915,16 +4918,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4974,7 +4977,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5003,10 +5006,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5032,10 +5035,10 @@
         <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5086,7 +5089,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5095,7 +5098,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -5115,10 +5118,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5227,10 +5230,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5341,10 +5344,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5457,10 +5460,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5486,10 +5489,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5519,10 +5522,10 @@
         <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>21</v>
@@ -5540,7 +5543,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5569,10 +5572,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5598,13 +5601,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5654,7 +5657,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5683,10 +5686,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5712,10 +5715,10 @@
         <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5766,7 +5769,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5795,10 +5798,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5824,10 +5827,10 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5878,7 +5881,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5907,10 +5910,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5936,10 +5939,10 @@
         <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5990,7 +5993,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6019,10 +6022,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6048,10 +6051,10 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6102,7 +6105,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6131,10 +6134,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6160,10 +6163,10 @@
         <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6214,7 +6217,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6223,7 +6226,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6243,10 +6246,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6355,10 +6358,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6469,10 +6472,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6585,10 +6588,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6614,10 +6617,10 @@
         <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6668,7 +6671,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6697,10 +6700,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6726,10 +6729,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6780,7 +6783,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6809,10 +6812,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6838,13 +6841,13 @@
         <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6894,7 +6897,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6923,10 +6926,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6952,13 +6955,13 @@
         <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7008,7 +7011,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7037,10 +7040,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7063,16 +7066,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7122,7 +7125,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7151,13 +7154,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>21</v>
@@ -7182,10 +7185,10 @@
         <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7248,7 +7251,7 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -7265,10 +7268,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7377,10 +7380,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7491,10 +7494,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7607,10 +7610,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7636,10 +7639,10 @@
         <v>21</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7690,7 +7693,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7719,10 +7722,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7730,7 +7733,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>87</v>
@@ -7748,13 +7751,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7804,7 +7807,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7833,14 +7836,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7859,13 +7862,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7916,7 +7919,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7934,7 +7937,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -7945,10 +7948,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7974,10 +7977,10 @@
         <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8028,7 +8031,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8037,7 +8040,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -8057,10 +8060,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8169,10 +8172,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8283,10 +8286,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8399,10 +8402,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8428,13 +8431,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8463,10 +8466,10 @@
         <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -8484,7 +8487,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8513,10 +8516,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8539,16 +8542,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8598,7 +8601,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8627,10 +8630,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8656,10 +8659,10 @@
         <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8710,7 +8713,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8719,7 +8722,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -8739,10 +8742,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8851,10 +8854,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8965,10 +8968,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9081,10 +9084,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9110,10 +9113,10 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9143,10 +9146,10 @@
         <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9164,7 +9167,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -9193,10 +9196,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9222,13 +9225,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9278,7 +9281,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9307,10 +9310,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9336,10 +9339,10 @@
         <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9390,7 +9393,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9419,10 +9422,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9448,10 +9451,10 @@
         <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9502,7 +9505,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9531,10 +9534,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9560,10 +9563,10 @@
         <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9614,7 +9617,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9643,10 +9646,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9672,10 +9675,10 @@
         <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9726,7 +9729,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9755,10 +9758,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9784,10 +9787,10 @@
         <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9838,7 +9841,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9847,7 +9850,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -9867,10 +9870,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9979,10 +9982,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10093,10 +10096,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10209,10 +10212,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10238,10 +10241,10 @@
         <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10292,7 +10295,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10321,10 +10324,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10350,10 +10353,10 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10404,7 +10407,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10433,10 +10436,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10462,13 +10465,13 @@
         <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10518,7 +10521,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10547,10 +10550,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10576,13 +10579,13 @@
         <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10632,7 +10635,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10661,10 +10664,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10687,16 +10690,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10746,7 +10749,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10775,13 +10778,13 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>21</v>
@@ -10806,10 +10809,10 @@
         <v>145</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10872,7 +10875,7 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
@@ -10889,10 +10892,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11001,10 +11004,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11115,10 +11118,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11231,10 +11234,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11260,10 +11263,10 @@
         <v>21</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11314,7 +11317,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11343,10 +11346,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11354,7 +11357,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>87</v>
@@ -11372,13 +11375,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11428,7 +11431,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11457,14 +11460,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11483,13 +11486,13 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11540,7 +11543,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11558,7 +11561,7 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
@@ -11569,10 +11572,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11598,10 +11601,10 @@
         <v>145</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11652,7 +11655,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11661,7 +11664,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -11681,10 +11684,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11793,10 +11796,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11907,10 +11910,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12023,10 +12026,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12052,13 +12055,13 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12087,10 +12090,10 @@
         <v>127</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
@@ -12108,7 +12111,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12137,10 +12140,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12163,16 +12166,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12222,7 +12225,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12251,10 +12254,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12280,10 +12283,10 @@
         <v>145</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12334,7 +12337,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12343,7 +12346,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12363,10 +12366,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12475,10 +12478,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12589,10 +12592,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12705,10 +12708,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12734,10 +12737,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12767,10 +12770,10 @@
         <v>127</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>21</v>
@@ -12788,7 +12791,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12817,10 +12820,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12846,13 +12849,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12902,7 +12905,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12931,10 +12934,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12960,10 +12963,10 @@
         <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13014,7 +13017,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13043,10 +13046,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13072,10 +13075,10 @@
         <v>132</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13126,7 +13129,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13155,10 +13158,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13184,10 +13187,10 @@
         <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13238,7 +13241,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13267,10 +13270,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13296,10 +13299,10 @@
         <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13350,7 +13353,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13379,10 +13382,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13408,10 +13411,10 @@
         <v>145</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13462,7 +13465,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13471,7 +13474,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -13491,10 +13494,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13603,10 +13606,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13717,10 +13720,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13833,10 +13836,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13862,10 +13865,10 @@
         <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13916,7 +13919,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13945,10 +13948,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13974,10 +13977,10 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14028,7 +14031,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14057,10 +14060,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14086,13 +14089,13 @@
         <v>150</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14142,7 +14145,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14171,10 +14174,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14200,13 +14203,13 @@
         <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14256,7 +14259,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14285,10 +14288,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14311,16 +14314,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14370,7 +14373,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14399,20 +14402,20 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>87</v>
@@ -14430,10 +14433,10 @@
         <v>145</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14496,7 +14499,7 @@
         <v>21</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>21</v>
@@ -14513,10 +14516,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14625,10 +14628,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14739,10 +14742,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14855,10 +14858,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14884,10 +14887,10 @@
         <v>21</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14938,7 +14941,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -14967,10 +14970,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14978,7 +14981,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>87</v>
@@ -14996,13 +14999,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15052,7 +15055,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15081,14 +15084,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15107,13 +15110,13 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15164,7 +15167,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15182,10 +15185,10 @@
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
@@ -15193,10 +15196,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15222,10 +15225,10 @@
         <v>145</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15276,7 +15279,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15285,7 +15288,7 @@
         <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>99</v>
@@ -15305,10 +15308,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15417,10 +15420,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15531,10 +15534,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15647,10 +15650,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15676,13 +15679,13 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15711,10 +15714,10 @@
         <v>127</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>21</v>
@@ -15732,7 +15735,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -15761,10 +15764,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15787,16 +15790,16 @@
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15846,7 +15849,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -15875,10 +15878,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15904,10 +15907,10 @@
         <v>145</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15958,7 +15961,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -15967,7 +15970,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -15987,10 +15990,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16099,10 +16102,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16213,10 +16216,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16329,10 +16332,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16358,10 +16361,10 @@
         <v>107</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16391,10 +16394,10 @@
         <v>127</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>21</v>
@@ -16412,7 +16415,7 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>87</v>
@@ -16441,10 +16444,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16470,13 +16473,13 @@
         <v>101</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -16526,7 +16529,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>87</v>
@@ -16555,10 +16558,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16584,10 +16587,10 @@
         <v>150</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -16638,7 +16641,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -16667,10 +16670,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16696,10 +16699,10 @@
         <v>132</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -16750,7 +16753,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -16779,10 +16782,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16808,10 +16811,10 @@
         <v>150</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -16862,7 +16865,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -16891,10 +16894,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16920,10 +16923,10 @@
         <v>150</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -16974,7 +16977,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17003,10 +17006,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17032,10 +17035,10 @@
         <v>145</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -17086,7 +17089,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17095,7 +17098,7 @@
         <v>87</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>99</v>
@@ -17115,10 +17118,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17227,10 +17230,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17341,10 +17344,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17457,10 +17460,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17486,10 +17489,10 @@
         <v>150</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -17540,7 +17543,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17569,10 +17572,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17598,10 +17601,10 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -17652,7 +17655,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -17681,10 +17684,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17710,13 +17713,13 @@
         <v>150</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -17766,7 +17769,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -17795,10 +17798,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17824,13 +17827,13 @@
         <v>132</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -17880,7 +17883,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -17909,10 +17912,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17935,16 +17938,16 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17994,7 +17997,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18023,20 +18026,20 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>175</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>79</v>
@@ -18054,10 +18057,10 @@
         <v>145</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18120,7 +18123,7 @@
         <v>21</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>21</v>
@@ -18137,10 +18140,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18249,10 +18252,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18363,10 +18366,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -18479,10 +18482,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18508,10 +18511,10 @@
         <v>21</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -18562,7 +18565,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -18591,10 +18594,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18602,7 +18605,7 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>87</v>
@@ -18620,13 +18623,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18676,7 +18679,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -18705,10 +18708,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18731,13 +18734,13 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18788,7 +18791,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -18803,10 +18806,10 @@
         <v>21</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>21</v>
@@ -18817,10 +18820,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18846,10 +18849,10 @@
         <v>145</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -18900,7 +18903,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -18909,7 +18912,7 @@
         <v>87</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>99</v>
@@ -18929,10 +18932,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19041,10 +19044,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19155,10 +19158,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19271,10 +19274,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19300,13 +19303,13 @@
         <v>107</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -19335,10 +19338,10 @@
         <v>127</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>21</v>
@@ -19356,7 +19359,7 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -19385,10 +19388,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19411,16 +19414,16 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -19470,7 +19473,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -19499,10 +19502,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19528,10 +19531,10 @@
         <v>145</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -19582,7 +19585,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -19591,7 +19594,7 @@
         <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>99</v>
@@ -19611,10 +19614,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19723,10 +19726,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19837,10 +19840,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19953,10 +19956,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19982,10 +19985,10 @@
         <v>107</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20015,10 +20018,10 @@
         <v>127</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>21</v>
@@ -20036,7 +20039,7 @@
         <v>21</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>87</v>
@@ -20065,10 +20068,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20094,13 +20097,13 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -20150,7 +20153,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>87</v>
@@ -20179,10 +20182,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20208,10 +20211,10 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -20262,7 +20265,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -20291,10 +20294,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20320,10 +20323,10 @@
         <v>132</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -20374,7 +20377,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -20403,10 +20406,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20432,10 +20435,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -20486,7 +20489,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -20515,10 +20518,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20544,10 +20547,10 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20598,7 +20601,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -20627,10 +20630,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20656,10 +20659,10 @@
         <v>145</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -20710,7 +20713,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -20719,7 +20722,7 @@
         <v>87</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>99</v>
@@ -20739,10 +20742,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20851,10 +20854,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20965,10 +20968,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21081,10 +21084,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21110,10 +21113,10 @@
         <v>150</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21164,7 +21167,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>87</v>
@@ -21193,10 +21196,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21222,10 +21225,10 @@
         <v>101</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -21276,7 +21279,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -21305,10 +21308,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21334,13 +21337,13 @@
         <v>150</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -21390,7 +21393,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
@@ -21419,10 +21422,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21448,13 +21451,13 @@
         <v>132</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -21504,7 +21507,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -21533,10 +21536,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21559,16 +21562,16 @@
         <v>88</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -21618,7 +21621,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -21647,10 +21650,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21673,19 +21676,19 @@
         <v>88</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>21</v>
@@ -21734,7 +21737,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation Medikationsplan-Searchset-Bundle Medikationsplan</t>
+    <t>AT ELGA e-Medikation Medikationsplan-Bundle Medikationsplan</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1233,7 +1233,7 @@
   </si>
   <si>
     <t>Practitioner {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner}
-Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole}Patient {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient}</t>
+Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole}</t>
   </si>
   <si>
     <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
@@ -1677,7 +1677,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.66796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="155.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2852,7 +2852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2868,10 +2868,10 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -379,7 +379,7 @@
 </t>
   </si>
   <si>
-    <t>Persistenter Identifikator für das Bundle.</t>
+    <t>Persistent identifier for the bundle</t>
   </si>
   <si>
     <t>A persistent identifier for the bundle that won't change as a bundle is copied from server to server.</t>
@@ -477,7 +477,7 @@
 </t>
   </si>
   <si>
-    <t>Verweise auf weiterführende Informationen zum Bundle.</t>
+    <t>Links related to this Bundle</t>
   </si>
   <si>
     <t>A series of links that provide context to this bundle.</t>
@@ -616,7 +616,7 @@
     <t>Bundle.entry.fullUrl</t>
   </si>
   <si>
-    <t>Eindeutige URL für den Eintrag im Bundle.</t>
+    <t>URI for resource (Absolute URL server address or URI for UUID/OID)</t>
   </si>
   <si>
     <t>The Absolute URL for the resource.  The fullUrl SHALL NOT disagree with the id in the resource - i.e. if the fullUrl is not a urn:uuid, the URL shall be version-independent URL consistent with the Resource.id. The fullUrl is a version independent reference to the resource. The fullUrl element SHALL have a value except that: 
@@ -2396,7 +2396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -2412,10 +2412,10 @@
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -2852,7 +2852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -3551,7 +3551,7 @@
         <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,11 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Bundle vom Typ Searchset bestehend aus: 
+    <t>Das Medikationsplan-Bundle vom Typ Searchset enthält: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus
-- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
+- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung
+- 1..1 Patient
+- 1..* Authors</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -428,7 +430,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Erstellung des Bundles.</t>
+    <t>When the bundle was assembled</t>
   </si>
   <si>
     <t>The date/time that the bundle was assembled - i.e. when the resources were placed in the bundle.</t>
@@ -2184,7 +2186,7 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -2624,7 +2626,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2637,13 +2639,13 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2642,7 +2642,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,11 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Medikationsplan-Bundle vom Typ Searchset enthält: 
-- 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus
-- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung
-- 1..1 Patient
-- 1..* Authors</t>
+    <t>Profil für den Medikationsplan als Ergebnis der $plan-read Operation.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6350" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6332" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -330,7 +330,7 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
+    <t>Fachliche Begründung: Die Ressource wird nach den Regeln dieses Implementierungsleitfadens interpretiert. Zusätzliche implizite Verarbeitungsregeln werden nicht verwendet.</t>
   </si>
   <si>
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
@@ -535,6 +535,68 @@
     <t>Bundle.link.modifierExtension</t>
   </si>
   <si>
+    <t>Fachliche Begründung: Es sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.link.relation</t>
+  </si>
+  <si>
+    <t>See http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1</t>
+  </si>
+  <si>
+    <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <t>Bundle.link.url</t>
+  </si>
+  <si>
+    <t>Reference details for the link</t>
+  </si>
+  <si>
+    <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>Bundle.entry</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Entry in the bundle - will have a resource or information</t>
+  </si>
+  <si>
+    <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:resource}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>Bundle.entry.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user contentmodifiers</t>
   </si>
@@ -547,59 +609,6 @@
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.link.relation</t>
-  </si>
-  <si>
-    <t>See http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1</t>
-  </si>
-  <si>
-    <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
-  </si>
-  <si>
-    <t>Bundle.link.url</t>
-  </si>
-  <si>
-    <t>Reference details for the link</t>
-  </si>
-  <si>
-    <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>Bundle.entry</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Entry in the bundle - will have a resource or information</t>
-  </si>
-  <si>
-    <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:resource}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>Bundle.entry.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry.modifierExtension</t>
   </si>
   <si>
     <t>Bundle.entry.link</t>
@@ -911,10 +920,16 @@
     <t>Bundle.entry:Medikationsplan.search.mode</t>
   </si>
   <si>
+    <t>match</t>
+  </si>
+  <si>
     <t>Bundle.entry:Medikationsplan.search.score</t>
   </si>
   <si>
     <t>Bundle.entry:Medikationsplan.request</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: In einem Searchset Bundle darf kein Request vorkommen.</t>
   </si>
   <si>
     <t>Bundle.entry:Medikationsplan.request.id</t>
@@ -1027,6 +1042,9 @@
     <t>Bundle.entry:Medikationsplaneintrag.search.mode</t>
   </si>
   <si>
+    <t>include</t>
+  </si>
+  <si>
     <t>Bundle.entry:Medikationsplaneintrag.search.score</t>
   </si>
   <si>
@@ -1231,7 +1249,7 @@
   </si>
   <si>
     <t>Practitioner {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner}
-Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole}</t>
+Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole}Organization {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-organization}</t>
   </si>
   <si>
     <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
@@ -1675,7 +1693,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="155.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="227.40625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2410,7 +2428,7 @@
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>21</v>
@@ -2850,7 +2868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -2863,13 +2881,13 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
@@ -3199,14 +3217,14 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -3221,17 +3239,13 @@
         <v>157</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
       </c>
@@ -3279,7 +3293,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3297,7 +3311,7 @@
         <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -3306,12 +3320,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3325,7 +3339,7 @@
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -3337,10 +3351,10 @@
         <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3352,7 +3366,7 @@
         <v>21</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>21</v>
@@ -3391,7 +3405,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3418,12 +3432,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3437,7 +3451,7 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -3449,10 +3463,10 @@
         <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3503,7 +3517,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3532,10 +3546,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3543,7 +3557,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -3561,10 +3575,10 @@
         <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3603,17 +3617,17 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3625,7 +3639,7 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
@@ -3642,10 +3656,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3754,10 +3768,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3868,14 +3882,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3897,16 +3911,16 @@
         <v>157</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3955,7 +3969,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3984,10 +3998,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3998,7 +4012,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -4013,10 +4027,10 @@
         <v>21</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4067,7 +4081,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4096,10 +4110,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4107,7 +4121,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>87</v>
@@ -4125,13 +4139,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4181,7 +4195,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4210,10 +4224,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4236,13 +4250,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4293,7 +4307,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4322,10 +4336,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4351,10 +4365,10 @@
         <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4405,7 +4419,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4414,7 +4428,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4434,10 +4448,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4546,10 +4560,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4660,14 +4674,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4689,16 +4703,16 @@
         <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4747,7 +4761,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4776,10 +4790,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4805,13 +4819,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4840,10 +4854,10 @@
         <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4861,7 +4875,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4890,10 +4904,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4916,16 +4930,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4975,7 +4989,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5004,10 +5018,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5033,10 +5047,10 @@
         <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5087,7 +5101,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5096,7 +5110,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -5116,10 +5130,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5228,10 +5242,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5342,14 +5356,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5371,16 +5385,16 @@
         <v>157</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5429,7 +5443,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5458,10 +5472,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5487,10 +5501,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5520,28 +5534,28 @@
         <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5570,10 +5584,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5599,13 +5613,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5655,7 +5669,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5684,10 +5698,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5713,10 +5727,10 @@
         <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5767,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5796,10 +5810,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5825,10 +5839,10 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5879,7 +5893,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5908,10 +5922,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5937,10 +5951,10 @@
         <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5991,7 +6005,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6020,10 +6034,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6049,10 +6063,10 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6103,7 +6117,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6132,10 +6146,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6161,10 +6175,10 @@
         <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6215,7 +6229,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6224,7 +6238,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6244,10 +6258,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6356,10 +6370,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6470,14 +6484,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6499,16 +6513,16 @@
         <v>157</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6557,7 +6571,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6586,10 +6600,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6615,10 +6629,10 @@
         <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6669,7 +6683,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6698,10 +6712,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6727,10 +6741,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6781,7 +6795,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6810,10 +6824,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6839,13 +6853,13 @@
         <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6895,7 +6909,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6924,10 +6938,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6953,13 +6967,13 @@
         <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7009,7 +7023,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7038,10 +7052,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7064,16 +7078,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7123,7 +7137,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7150,15 +7164,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>21</v>
@@ -7171,7 +7185,7 @@
         <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>21</v>
@@ -7183,10 +7197,10 @@
         <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7237,7 +7251,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7249,7 +7263,7 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -7266,10 +7280,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7378,10 +7392,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7492,21 +7506,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7521,17 +7535,13 @@
         <v>157</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7579,7 +7589,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7597,7 +7607,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7608,10 +7618,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7622,7 +7632,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7634,13 +7644,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7691,7 +7701,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7718,12 +7728,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7737,7 +7747,7 @@
         <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -7749,13 +7759,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7805,7 +7815,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7832,16 +7842,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7851,7 +7861,7 @@
         <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -7860,13 +7870,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7917,7 +7927,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7935,7 +7945,7 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -7944,12 +7954,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7957,13 +7967,13 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>21</v>
@@ -7975,10 +7985,10 @@
         <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8029,7 +8039,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8038,7 +8048,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -8058,10 +8068,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8170,10 +8180,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8284,21 +8294,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -8313,17 +8323,13 @@
         <v>157</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8371,7 +8377,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8389,7 +8395,7 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
@@ -8398,12 +8404,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8411,13 +8417,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -8429,13 +8435,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8446,7 +8452,7 @@
         <v>21</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>21</v>
@@ -8464,10 +8470,10 @@
         <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -8485,7 +8491,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8514,10 +8520,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8540,16 +8546,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8599,7 +8605,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8626,12 +8632,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8642,10 +8648,10 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -8657,10 +8663,10 @@
         <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8711,7 +8717,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8720,7 +8726,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -8740,10 +8746,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8852,10 +8858,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8966,14 +8972,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8995,16 +9001,16 @@
         <v>157</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9053,7 +9059,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9082,10 +9088,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9111,10 +9117,10 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9144,28 +9150,28 @@
         <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -9194,10 +9200,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9223,13 +9229,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9279,7 +9285,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9308,10 +9314,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9337,10 +9343,10 @@
         <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9391,7 +9397,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9420,10 +9426,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9449,10 +9455,10 @@
         <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9503,7 +9509,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9532,10 +9538,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9561,10 +9567,10 @@
         <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9615,7 +9621,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9644,10 +9650,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9673,10 +9679,10 @@
         <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9727,7 +9733,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9756,10 +9762,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9785,10 +9791,10 @@
         <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9839,7 +9845,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9848,7 +9854,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -9868,10 +9874,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9980,10 +9986,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10094,14 +10100,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10123,16 +10129,16 @@
         <v>157</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10181,7 +10187,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10210,10 +10216,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10239,10 +10245,10 @@
         <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10293,7 +10299,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10322,10 +10328,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10351,10 +10357,10 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10405,7 +10411,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10434,10 +10440,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10463,13 +10469,13 @@
         <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10519,7 +10525,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10548,10 +10554,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10577,13 +10583,13 @@
         <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10633,7 +10639,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10662,10 +10668,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10688,16 +10694,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10747,7 +10753,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10774,15 +10780,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>21</v>
@@ -10795,7 +10801,7 @@
         <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>21</v>
@@ -10807,10 +10813,10 @@
         <v>145</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10861,7 +10867,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10873,7 +10879,7 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
@@ -10890,10 +10896,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11002,10 +11008,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11116,21 +11122,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
@@ -11145,17 +11151,13 @@
         <v>157</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11203,7 +11205,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11221,7 +11223,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -11232,10 +11234,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11246,7 +11248,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>21</v>
@@ -11258,13 +11260,13 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11315,7 +11317,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11342,12 +11344,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11361,7 +11363,7 @@
         <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>21</v>
@@ -11373,13 +11375,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11429,7 +11431,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11456,16 +11458,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11475,7 +11477,7 @@
         <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>21</v>
@@ -11484,13 +11486,13 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11541,7 +11543,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11559,7 +11561,7 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
@@ -11568,12 +11570,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11581,13 +11583,13 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>21</v>
@@ -11599,10 +11601,10 @@
         <v>145</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11653,7 +11655,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11662,7 +11664,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -11682,10 +11684,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11794,10 +11796,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11908,21 +11910,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>21</v>
@@ -11937,17 +11939,13 @@
         <v>157</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>21</v>
       </c>
@@ -11995,7 +11993,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12013,7 +12011,7 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>21</v>
@@ -12022,12 +12020,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12035,13 +12033,13 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>21</v>
@@ -12053,13 +12051,13 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12070,7 +12068,7 @@
         <v>21</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>21</v>
@@ -12088,10 +12086,10 @@
         <v>127</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
@@ -12109,7 +12107,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12138,10 +12136,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12164,16 +12162,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12223,7 +12221,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12250,12 +12248,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12266,10 +12264,10 @@
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>21</v>
@@ -12281,10 +12279,10 @@
         <v>145</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12335,7 +12333,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12344,7 +12342,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12364,10 +12362,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12476,10 +12474,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12590,14 +12588,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12619,16 +12617,16 @@
         <v>157</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -12677,7 +12675,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12706,10 +12704,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12735,10 +12733,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12768,28 +12766,28 @@
         <v>127</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12818,10 +12816,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12847,13 +12845,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12903,7 +12901,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12932,10 +12930,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12961,10 +12959,10 @@
         <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13015,7 +13013,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13044,10 +13042,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13073,10 +13071,10 @@
         <v>132</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13127,7 +13125,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13156,10 +13154,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13185,10 +13183,10 @@
         <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13239,7 +13237,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13268,10 +13266,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13297,10 +13295,10 @@
         <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13351,7 +13349,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13380,10 +13378,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13409,10 +13407,10 @@
         <v>145</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13463,7 +13461,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13472,7 +13470,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -13492,10 +13490,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13604,10 +13602,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13718,14 +13716,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13747,16 +13745,16 @@
         <v>157</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -13805,7 +13803,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13834,10 +13832,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13863,10 +13861,10 @@
         <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -13917,7 +13915,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13946,10 +13944,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13975,10 +13973,10 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14029,7 +14027,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14058,10 +14056,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14087,13 +14085,13 @@
         <v>150</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14143,7 +14141,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14172,10 +14170,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14201,13 +14199,13 @@
         <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14257,7 +14255,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14286,10 +14284,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14312,16 +14310,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14371,7 +14369,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14398,15 +14396,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>21</v>
@@ -14419,7 +14417,7 @@
         <v>87</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>21</v>
@@ -14431,10 +14429,10 @@
         <v>145</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -14485,7 +14483,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14497,7 +14495,7 @@
         <v>21</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>21</v>
@@ -14514,10 +14512,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14626,10 +14624,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14740,21 +14738,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>21</v>
@@ -14769,17 +14767,13 @@
         <v>157</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M116" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
@@ -14827,7 +14821,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -14845,7 +14839,7 @@
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>21</v>
@@ -14856,10 +14850,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14870,7 +14864,7 @@
         <v>78</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>21</v>
@@ -14882,13 +14876,13 @@
         <v>88</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14939,7 +14933,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -14966,12 +14960,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14985,7 +14979,7 @@
         <v>87</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>21</v>
@@ -14997,13 +14991,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15053,7 +15047,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15080,16 +15074,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15099,7 +15093,7 @@
         <v>87</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>21</v>
@@ -15108,13 +15102,13 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15165,7 +15159,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15183,21 +15177,21 @@
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15205,13 +15199,13 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>21</v>
@@ -15223,10 +15217,10 @@
         <v>145</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15277,7 +15271,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15286,7 +15280,7 @@
         <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>99</v>
@@ -15306,10 +15300,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15418,10 +15412,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15532,21 +15526,21 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>21</v>
@@ -15561,17 +15555,13 @@
         <v>157</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M123" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>21</v>
       </c>
@@ -15619,7 +15609,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -15637,7 +15627,7 @@
         <v>21</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>21</v>
@@ -15646,12 +15636,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15659,13 +15649,13 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>21</v>
@@ -15677,13 +15667,13 @@
         <v>107</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15694,7 +15684,7 @@
         <v>21</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>21</v>
@@ -15712,10 +15702,10 @@
         <v>127</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>21</v>
@@ -15733,7 +15723,7 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -15762,10 +15752,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15788,16 +15778,16 @@
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -15847,7 +15837,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -15874,12 +15864,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15890,10 +15880,10 @@
         <v>78</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>21</v>
@@ -15905,10 +15895,10 @@
         <v>145</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -15959,7 +15949,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -15968,7 +15958,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -15988,10 +15978,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16100,10 +16090,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16214,14 +16204,14 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -16243,16 +16233,16 @@
         <v>157</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -16301,7 +16291,7 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>78</v>
@@ -16330,10 +16320,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16359,10 +16349,10 @@
         <v>107</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -16392,28 +16382,28 @@
         <v>127</v>
       </c>
       <c r="Y130" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF130" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>87</v>
@@ -16442,10 +16432,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16471,13 +16461,13 @@
         <v>101</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -16527,7 +16517,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>87</v>
@@ -16556,10 +16546,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16585,10 +16575,10 @@
         <v>150</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -16639,7 +16629,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -16668,10 +16658,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16697,10 +16687,10 @@
         <v>132</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -16751,7 +16741,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -16780,10 +16770,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16809,10 +16799,10 @@
         <v>150</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -16863,7 +16853,7 @@
         <v>21</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -16892,10 +16882,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16921,10 +16911,10 @@
         <v>150</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -16975,7 +16965,7 @@
         <v>21</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17004,10 +16994,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17033,10 +17023,10 @@
         <v>145</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -17087,7 +17077,7 @@
         <v>21</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -17096,7 +17086,7 @@
         <v>87</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AJ136" t="s" s="2">
         <v>99</v>
@@ -17116,10 +17106,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17228,10 +17218,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17342,14 +17332,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -17371,16 +17361,16 @@
         <v>157</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>21</v>
@@ -17429,7 +17419,7 @@
         <v>21</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -17458,10 +17448,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17487,10 +17477,10 @@
         <v>150</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -17541,7 +17531,7 @@
         <v>21</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -17570,10 +17560,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17599,10 +17589,10 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -17653,7 +17643,7 @@
         <v>21</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -17682,10 +17672,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17711,13 +17701,13 @@
         <v>150</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -17767,7 +17757,7 @@
         <v>21</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -17796,10 +17786,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17825,13 +17815,13 @@
         <v>132</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -17881,7 +17871,7 @@
         <v>21</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -17910,10 +17900,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17936,16 +17926,16 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -17995,7 +17985,7 @@
         <v>21</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -18022,15 +18012,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" hidden="true">
+    <row r="145">
       <c r="A145" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>21</v>
@@ -18043,7 +18033,7 @@
         <v>79</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>21</v>
@@ -18055,10 +18045,10 @@
         <v>145</v>
       </c>
       <c r="L145" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M145" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M145" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -18109,7 +18099,7 @@
         <v>21</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -18121,7 +18111,7 @@
         <v>21</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>21</v>
@@ -18138,10 +18128,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18250,10 +18240,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18364,21 +18354,21 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>21</v>
@@ -18393,17 +18383,13 @@
         <v>157</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M148" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>21</v>
       </c>
@@ -18451,7 +18437,7 @@
         <v>21</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -18469,7 +18455,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>
@@ -18480,10 +18466,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18494,7 +18480,7 @@
         <v>78</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>21</v>
@@ -18506,13 +18492,13 @@
         <v>88</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -18563,7 +18549,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -18590,12 +18576,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18609,7 +18595,7 @@
         <v>87</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>21</v>
@@ -18621,13 +18607,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18677,7 +18663,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -18704,12 +18690,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18723,7 +18709,7 @@
         <v>87</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>21</v>
@@ -18732,13 +18718,13 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18789,7 +18775,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -18804,10 +18790,10 @@
         <v>21</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>21</v>
@@ -18816,12 +18802,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18829,13 +18815,13 @@
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>21</v>
@@ -18847,10 +18833,10 @@
         <v>145</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -18901,7 +18887,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -18910,7 +18896,7 @@
         <v>87</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>99</v>
@@ -18930,10 +18916,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19042,10 +19028,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19156,21 +19142,21 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>164</v>
+        <v>21</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>21</v>
@@ -19185,17 +19171,13 @@
         <v>157</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M155" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M155" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>21</v>
       </c>
@@ -19243,7 +19225,7 @@
         <v>21</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -19261,7 +19243,7 @@
         <v>21</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM155" t="s" s="2">
         <v>21</v>
@@ -19270,12 +19252,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -19283,13 +19265,13 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>21</v>
@@ -19301,13 +19283,13 @@
         <v>107</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -19318,7 +19300,7 @@
         <v>21</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>21</v>
@@ -19336,10 +19318,10 @@
         <v>127</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>21</v>
@@ -19357,7 +19339,7 @@
         <v>21</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -19386,10 +19368,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -19412,16 +19394,16 @@
         <v>88</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -19471,7 +19453,7 @@
         <v>21</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -19498,12 +19480,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19514,10 +19496,10 @@
         <v>78</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>21</v>
@@ -19529,10 +19511,10 @@
         <v>145</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>215</v>
+        <v>290</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -19583,7 +19565,7 @@
         <v>21</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -19592,7 +19574,7 @@
         <v>87</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>99</v>
@@ -19612,10 +19594,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19724,10 +19706,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19838,14 +19820,14 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -19867,16 +19849,16 @@
         <v>157</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -19925,7 +19907,7 @@
         <v>21</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -19954,10 +19936,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19983,10 +19965,10 @@
         <v>107</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -20016,28 +19998,28 @@
         <v>127</v>
       </c>
       <c r="Y162" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF162" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>87</v>
@@ -20066,10 +20048,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20095,13 +20077,13 @@
         <v>101</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -20151,7 +20133,7 @@
         <v>21</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>87</v>
@@ -20180,10 +20162,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -20209,10 +20191,10 @@
         <v>150</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -20263,7 +20245,7 @@
         <v>21</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -20292,10 +20274,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -20321,10 +20303,10 @@
         <v>132</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -20375,7 +20357,7 @@
         <v>21</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -20404,10 +20386,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -20433,10 +20415,10 @@
         <v>150</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -20487,7 +20469,7 @@
         <v>21</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -20516,10 +20498,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -20545,10 +20527,10 @@
         <v>150</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -20599,7 +20581,7 @@
         <v>21</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -20628,10 +20610,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -20657,10 +20639,10 @@
         <v>145</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -20711,7 +20693,7 @@
         <v>21</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -20720,7 +20702,7 @@
         <v>87</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>99</v>
@@ -20740,10 +20722,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20852,10 +20834,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20966,14 +20948,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -20995,16 +20977,16 @@
         <v>157</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -21053,7 +21035,7 @@
         <v>21</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -21082,10 +21064,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21111,10 +21093,10 @@
         <v>150</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -21165,7 +21147,7 @@
         <v>21</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>87</v>
@@ -21194,10 +21176,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -21223,10 +21205,10 @@
         <v>101</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -21277,7 +21259,7 @@
         <v>21</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>78</v>
@@ -21306,10 +21288,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -21335,13 +21317,13 @@
         <v>150</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
@@ -21391,7 +21373,7 @@
         <v>21</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>78</v>
@@ -21420,10 +21402,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -21449,13 +21431,13 @@
         <v>132</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -21505,7 +21487,7 @@
         <v>21</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>78</v>
@@ -21534,10 +21516,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -21560,16 +21542,16 @@
         <v>88</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -21619,7 +21601,7 @@
         <v>21</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>78</v>
@@ -21648,10 +21630,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -21674,19 +21656,19 @@
         <v>88</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>21</v>
@@ -21735,7 +21717,7 @@
         <v>21</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>78</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6332" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6338" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -597,20 +597,6 @@
     <t>Bundle.entry.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
     <t>Bundle.entry.link</t>
   </si>
   <si>
@@ -670,6 +656,20 @@
     <t>Bundle.entry.search.modifierExtension</t>
   </si>
   <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
     <t>Bundle.entry.search.mode</t>
   </si>
   <si>
@@ -1133,7 +1133,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient}
+    <t xml:space="preserve">Patient {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-patient}
 </t>
   </si>
   <si>
@@ -1248,8 +1248,8 @@
     <t>Bundle.entry:Authors.resource</t>
   </si>
   <si>
-    <t>Practitioner {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner}
-Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole}Organization {https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-organization}</t>
+    <t>Practitioner {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner}
+Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole}Organization {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-organization}</t>
   </si>
   <si>
     <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
@@ -1693,7 +1693,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="227.40625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="231.0546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2754,7 +2754,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
@@ -2767,13 +2767,13 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
@@ -3889,14 +3889,14 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3911,17 +3911,13 @@
         <v>157</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3987,7 +3983,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -3998,10 +3994,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4027,10 +4023,10 @@
         <v>21</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4081,7 +4077,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4110,10 +4106,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4139,13 +4135,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4195,7 +4191,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4224,10 +4220,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4250,13 +4246,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4307,7 +4303,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4336,10 +4332,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4365,10 +4361,10 @@
         <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4419,7 +4415,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4428,7 +4424,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4448,10 +4444,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4560,10 +4556,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4674,14 +4670,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4703,16 +4699,16 @@
         <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5363,7 +5359,7 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5385,16 +5381,16 @@
         <v>157</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -6491,7 +6487,7 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6513,16 +6509,16 @@
         <v>157</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7078,7 +7074,7 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>266</v>
@@ -7513,14 +7509,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7535,13 +7531,17 @@
         <v>157</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7621,7 +7621,7 @@
         <v>274</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7647,10 +7647,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7701,7 +7701,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7733,7 +7733,7 @@
         <v>275</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7759,13 +7759,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7815,7 +7815,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7847,7 +7847,7 @@
         <v>276</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7927,7 +7927,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7959,7 +7959,7 @@
         <v>282</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7985,10 +7985,10 @@
         <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8039,7 +8039,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8048,7 +8048,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -8071,7 +8071,7 @@
         <v>283</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8183,7 +8183,7 @@
         <v>284</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8297,7 +8297,7 @@
         <v>285</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9001,16 +9001,16 @@
         <v>157</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10129,16 +10129,16 @@
         <v>157</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>21</v>
@@ -10694,7 +10694,7 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>266</v>
@@ -11129,14 +11129,14 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
@@ -11151,13 +11151,17 @@
         <v>157</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11223,7 +11227,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -11237,7 +11241,7 @@
         <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11263,10 +11267,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11317,7 +11321,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11349,7 +11353,7 @@
         <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11375,13 +11379,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11431,7 +11435,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11463,7 +11467,7 @@
         <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11543,7 +11547,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11575,7 +11579,7 @@
         <v>322</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11601,10 +11605,10 @@
         <v>145</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11655,7 +11659,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11664,7 +11668,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -11687,7 +11691,7 @@
         <v>323</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11799,7 +11803,7 @@
         <v>324</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11913,7 +11917,7 @@
         <v>325</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12595,7 +12599,7 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12617,16 +12621,16 @@
         <v>157</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>21</v>
@@ -13723,7 +13727,7 @@
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13745,16 +13749,16 @@
         <v>157</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>21</v>
@@ -14310,7 +14314,7 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>266</v>
@@ -14745,14 +14749,14 @@
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>21</v>
@@ -14767,13 +14771,17 @@
         <v>157</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
@@ -14839,7 +14847,7 @@
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>21</v>
@@ -14853,7 +14861,7 @@
         <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14879,10 +14887,10 @@
         <v>80</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14933,7 +14941,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -14965,7 +14973,7 @@
         <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14991,13 +14999,13 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15047,7 +15055,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -15079,7 +15087,7 @@
         <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15159,7 +15167,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -15191,7 +15199,7 @@
         <v>362</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15217,10 +15225,10 @@
         <v>145</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15271,7 +15279,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15280,7 +15288,7 @@
         <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>99</v>
@@ -15303,7 +15311,7 @@
         <v>363</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15415,7 +15423,7 @@
         <v>364</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15529,7 +15537,7 @@
         <v>365</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16211,7 +16219,7 @@
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
@@ -16233,16 +16241,16 @@
         <v>157</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -17339,7 +17347,7 @@
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -17361,16 +17369,16 @@
         <v>157</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>21</v>
@@ -17926,7 +17934,7 @@
         <v>88</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L144" t="s" s="2">
         <v>266</v>
@@ -18361,14 +18369,14 @@
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>21</v>
@@ -18383,13 +18391,17 @@
         <v>157</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N148" s="2"/>
-      <c r="O148" s="2"/>
+        <v>204</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>21</v>
       </c>
@@ -18455,7 +18467,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>
@@ -18469,7 +18481,7 @@
         <v>392</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18495,10 +18507,10 @@
         <v>80</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -18549,7 +18561,7 @@
         <v>21</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -18581,7 +18593,7 @@
         <v>393</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18607,13 +18619,13 @@
         <v>101</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18663,7 +18675,7 @@
         <v>21</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -18695,7 +18707,7 @@
         <v>394</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18775,7 +18787,7 @@
         <v>21</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -18807,7 +18819,7 @@
         <v>400</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18833,10 +18845,10 @@
         <v>145</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -18887,7 +18899,7 @@
         <v>21</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -18896,7 +18908,7 @@
         <v>87</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>99</v>
@@ -18919,7 +18931,7 @@
         <v>401</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19031,7 +19043,7 @@
         <v>402</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19145,7 +19157,7 @@
         <v>403</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19827,7 +19839,7 @@
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -19849,16 +19861,16 @@
         <v>157</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>21</v>
@@ -20955,7 +20967,7 @@
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -20977,16 +20989,16 @@
         <v>157</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>160</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>21</v>
@@ -21542,7 +21554,7 @@
         <v>88</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L176" t="s" s="2">
         <v>266</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1018,7 +1018,7 @@
 </t>
   </si>
   <si>
-    <t>Planeintrag</t>
+    <t>Ordering of medication for patient or group</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1249,7 +1249,7 @@
   </si>
   <si>
     <t>Practitioner {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner}
-Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole}Organization {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-organization}</t>
+Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole}</t>
   </si>
   <si>
     <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
@@ -1693,7 +1693,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="231.0546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="157.21484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6338" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6330" uniqueCount="431">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7509,14 +7509,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7531,17 +7531,13 @@
         <v>157</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -7607,7 +7603,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -11129,14 +11125,14 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>21</v>
@@ -11151,17 +11147,13 @@
         <v>157</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
@@ -11227,7 +11219,7 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>21</v>
@@ -14749,14 +14741,14 @@
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>21</v>
@@ -14771,17 +14763,13 @@
         <v>157</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
@@ -14847,7 +14835,7 @@
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>21</v>
@@ -18369,14 +18357,14 @@
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>21</v>
@@ -18391,17 +18379,13 @@
         <v>157</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>21</v>
       </c>
@@ -18467,7 +18451,7 @@
         <v>21</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1249,7 +1249,7 @@
   </si>
   <si>
     <t>Practitioner {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitioner}
-Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole}</t>
+Device {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-device-fachanwendung}PractitionerRole {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-practitionerrole}Organization {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-organization}</t>
   </si>
   <si>
     <t>A person with a  formal responsibility in the provisioning of healthcare or related services</t>
@@ -1693,7 +1693,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="157.21484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="231.0546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplan.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
